--- a/tests/fixtures/corpus/shape.xlsx
+++ b/tests/fixtures/corpus/shape.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10AAF093-74FD-49F5-845E-CEDE7EEE0664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{136203C1-CB57-4063-86A4-E8463E1366E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="16200" windowHeight="9307" xr2:uid="{925615F5-21EC-42E1-8CF9-B395112FDAD7}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="16200" windowHeight="9307" xr2:uid="{590D6C74-EC5E-4D18-8B7E-F5D4C73B6F17}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -116,7 +116,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AB630BA-EEDE-595B-F9A3-4B8A68D5F72C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F199E56-6035-BF1D-AE69-0AB2230B288A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -186,7 +186,7 @@
         <xdr:cNvPr id="3" name="Rectangle 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8241D671-5378-B763-AF0A-814754066EA2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7A244C4-0551-1678-D33D-C114651F11EC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -547,7 +547,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED499D90-F20E-4D64-A632-AF507209F690}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE425F65-5805-4357-84B3-2B1CC68B5EFB}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData>
